--- a/politis/content/politis-content.xlsx
+++ b/politis/content/politis-content.xlsx
@@ -139,7 +139,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="147">
   <si>
-    <t>Politis — Περιεχόμενο εφαρμογής</t>
+    <t>Ξεμπέρδεψα — Περιεχόμενο εφαρμογής</t>
   </si>
   <si>
     <t/>
